--- a/projects/zion-glamping-line/interno/ZION_ORCAMENTO_SC_Casulo_Safari_Lodge.xlsx
+++ b/projects/zion-glamping-line/interno/ZION_ORCAMENTO_SC_Casulo_Safari_Lodge.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1219,19 +1219,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B01-E</t>
+          <t>B09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arco A1, perna esquerda</t>
+          <t>Bico: cumeeira em balanço (de A1 à ponta, 2,40 m além de A0)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tubo Ø88,9 x 3,6 calandrado (elipse)</t>
+          <t>Tubo Ø114,3 x 4,0 curvado (ponta erguida 0,30 m)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1250,22 +1250,22 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>29.7</v>
+        <v>45.4</v>
       </c>
       <c r="K13" t="n">
-        <v>29.7</v>
+        <v>45.4</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
+          <t>Calandra suave + chapas de engaste soldadas</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
+          <t>Engaste em A0 e A1 por chapas 10 mm + 4 M16 cada (nó de momento) ⚠️</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1273,26 +1273,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Pórtico elíptico A1 (x = 1.65 m)</t>
+          <t>Sustenta a ponta do Bico em balanço sobre o deck</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B01-C</t>
+          <t>B10-E</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Arco A1, coroa (segmento superior)</t>
+          <t>Bico: tubo de borda esquerdo (ponta → anel A0)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7</v>
+        <v>4.24</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tubo Ø88,9 x 3,6 calandrado (elipse)</t>
+          <t>Tubo Ø60,3 x 3,0 curvado em 3D</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1311,22 +1311,22 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>28</v>
+        <v>18.8</v>
       </c>
       <c r="K14" t="n">
-        <v>28</v>
+        <v>18.8</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Calandra CNC; talões D03 das terças soldados</t>
+          <t>Curvamento CNC por gabarito 3D + ponteiras</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Encaixa nas luvas D02 das duas pernas</t>
+          <t>Nó soldado na ponta (B09) + chapa D01-B no anel A0 (2 M12)</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1334,26 +1334,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
+          <t>Borda rígida do Bico; recebe o keder da membrana</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B01-D</t>
+          <t>B10-D</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arco A1, perna direita</t>
+          <t>Bico: tubo de borda direito</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.93</v>
+        <v>4.24</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tubo Ø88,9 x 3,6 calandrado (elipse)</t>
+          <t>Tubo Ø60,3 x 3,0 curvado em 3D</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1372,17 +1372,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>29.7</v>
+        <v>18.8</v>
       </c>
       <c r="K15" t="n">
-        <v>29.7</v>
+        <v>18.8</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Idem perna esquerda</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1402,19 +1402,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B02-E</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arco A2, perna esquerda</t>
+          <t>Bico: costela intermediária (a 50 % do balanço)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.96</v>
+        <v>6.98</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tubo Ø88,9 x 3,6 calandrado (elipse)</t>
+          <t>Tubo Ø48,3 x 3,0 curvado</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1433,49 +1433,49 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
+          <t>Curvamento CNC + ponteiras M16</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
+          <t>Talão D03 na cumeeira e nas bordas</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Pórtico elíptico A2 (x = 2.85 m)</t>
+          <t>Trava as bordas e dá forma à membrana do Bico</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B02-C</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arco A2, coroa (segmento superior)</t>
+          <t>Bico: tirante Ø12 inox (cumeeira a 60 % → anel A0 a ±0,80 rad)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3.73</v>
+        <v>2.58</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1485,58 +1485,58 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tubo Ø88,9 x 3,6 calandrado (elipse)</t>
+          <t>Cabo inox AISI 316 Ø12 7 x 19</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ASTM A500 Gr. B galv.</t>
+          <t>inox 316</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>28.2</v>
+        <v>2.4</v>
       </c>
       <c r="K17" t="n">
-        <v>28.2</v>
+        <v>4.8</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Calandra CNC; talões D03 das terças soldados</t>
+          <t>Terminais prensados com olhal</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Encaixa nas luvas D02 das duas pernas</t>
+          <t>Olhal D05 + manilha + esticador M16 inox</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
+          <t>Reduz a flecha e a vibração da ponta em balanço ⚠️</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B02-D</t>
+          <t>B01-E</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arco A2, perna direita</t>
+          <t>Arco A1, perna esquerda</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1558,19 +1558,19 @@
         <v>3.6</v>
       </c>
       <c r="J18" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="K18" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Idem perna esquerda</t>
+          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1578,26 +1578,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Pórtico elíptico A1 (x = 1.65 m)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B03-E</t>
+          <t>B01-C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arco A3, perna esquerda</t>
+          <t>Arco A1, coroa (segmento superior)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1619,19 +1619,19 @@
         <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>29.9</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>29.9</v>
+        <v>28</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
+          <t>Calandra CNC; talões D03 das terças soldados</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
+          <t>Encaixa nas luvas D02 das duas pernas</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1639,26 +1639,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Pórtico elíptico A3 (x = 4.05 m)</t>
+          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B03-C</t>
+          <t>B01-D</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arco A3, coroa (segmento superior)</t>
+          <t>Arco A1, perna direita</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.72</v>
+        <v>3.93</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1680,19 +1680,19 @@
         <v>3.6</v>
       </c>
       <c r="J20" t="n">
-        <v>28.2</v>
+        <v>29.7</v>
       </c>
       <c r="K20" t="n">
-        <v>28.2</v>
+        <v>29.7</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Calandra CNC; talões D03 das terças soldados</t>
+          <t>Idem perna esquerda</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Encaixa nas luvas D02 das duas pernas</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -1700,26 +1700,26 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
+          <t>Idem</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B03-D</t>
+          <t>B02-E</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arco A3, perna direita</t>
+          <t>Arco A2, perna esquerda</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1741,19 +1741,19 @@
         <v>3.6</v>
       </c>
       <c r="J21" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Idem perna esquerda</t>
+          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -1761,26 +1761,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Pórtico elíptico A2 (x = 2.85 m)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B04-E</t>
+          <t>B02-C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arco A4, perna esquerda</t>
+          <t>Arco A2, coroa (segmento superior)</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.87</v>
+        <v>3.73</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1802,19 +1802,19 @@
         <v>3.6</v>
       </c>
       <c r="J22" t="n">
-        <v>29.3</v>
+        <v>28.2</v>
       </c>
       <c r="K22" t="n">
-        <v>29.3</v>
+        <v>28.2</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
+          <t>Calandra CNC; talões D03 das terças soldados</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
+          <t>Encaixa nas luvas D02 das duas pernas</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -1822,26 +1822,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Pórtico elíptico A4 (x = 5.25 m)</t>
+          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B04-C</t>
+          <t>B02-D</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arco A4, coroa (segmento superior)</t>
+          <t>Arco A2, perna direita</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.64</v>
+        <v>3.96</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1863,19 +1863,19 @@
         <v>3.6</v>
       </c>
       <c r="J23" t="n">
-        <v>27.6</v>
+        <v>30</v>
       </c>
       <c r="K23" t="n">
-        <v>27.6</v>
+        <v>30</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Calandra CNC; talões D03 das terças soldados</t>
+          <t>Idem perna esquerda</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Encaixa nas luvas D02 das duas pernas</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -1883,26 +1883,26 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
+          <t>Idem</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B04-D</t>
+          <t>B03-E</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arco A4, perna direita</t>
+          <t>Arco A3, perna esquerda</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1924,19 +1924,19 @@
         <v>3.6</v>
       </c>
       <c r="J24" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="K24" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Idem perna esquerda</t>
+          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -1944,26 +1944,26 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Pórtico elíptico A3 (x = 4.05 m)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B05-E</t>
+          <t>B03-C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Arco A5, perna esquerda</t>
+          <t>Arco A3, coroa (segmento superior)</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1985,19 +1985,19 @@
         <v>3.6</v>
       </c>
       <c r="J25" t="n">
-        <v>27.9</v>
+        <v>28.2</v>
       </c>
       <c r="K25" t="n">
-        <v>27.9</v>
+        <v>28.2</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
+          <t>Calandra CNC; talões D03 das terças soldados</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
+          <t>Encaixa nas luvas D02 das duas pernas</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -2005,26 +2005,26 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Pórtico elíptico A5 (x = 6.45 m)</t>
+          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B05-C</t>
+          <t>B03-D</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arco A5, coroa (segmento superior)</t>
+          <t>Arco A3, perna direita</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.46</v>
+        <v>3.95</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2046,19 +2046,19 @@
         <v>3.6</v>
       </c>
       <c r="J26" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="K26" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Calandra CNC; talões D03 das terças soldados</t>
+          <t>Idem perna esquerda</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Encaixa nas luvas D02 das duas pernas</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -2066,26 +2066,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
+          <t>Idem</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B05-D</t>
+          <t>B04-E</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Arco A5, perna direita</t>
+          <t>Arco A4, perna esquerda</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3.68</v>
+        <v>3.87</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2107,19 +2107,19 @@
         <v>3.6</v>
       </c>
       <c r="J27" t="n">
-        <v>27.9</v>
+        <v>29.3</v>
       </c>
       <c r="K27" t="n">
-        <v>27.9</v>
+        <v>29.3</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Idem perna esquerda</t>
+          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -2127,26 +2127,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Pórtico elíptico A4 (x = 5.25 m)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B06-E</t>
+          <t>B04-C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Arco A6, perna esquerda</t>
+          <t>Arco A4, coroa (segmento superior)</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2168,19 +2168,19 @@
         <v>3.6</v>
       </c>
       <c r="J28" t="n">
-        <v>25.1</v>
+        <v>27.6</v>
       </c>
       <c r="K28" t="n">
-        <v>25.1</v>
+        <v>27.6</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
+          <t>Calandra CNC; talões D03 das terças soldados</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
+          <t>Encaixa nas luvas D02 das duas pernas</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -2188,26 +2188,26 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Pórtico elíptico A6 (x = 7.65 m)</t>
+          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B06-C</t>
+          <t>B04-D</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Arco A6, coroa (segmento superior)</t>
+          <t>Arco A4, perna direita</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3.12</v>
+        <v>3.87</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2229,19 +2229,19 @@
         <v>3.6</v>
       </c>
       <c r="J29" t="n">
-        <v>23.6</v>
+        <v>29.3</v>
       </c>
       <c r="K29" t="n">
-        <v>23.6</v>
+        <v>29.3</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Calandra CNC; talões D03 das terças soldados</t>
+          <t>Idem perna esquerda</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Encaixa nas luvas D02 das duas pernas</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -2249,26 +2249,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
+          <t>Idem</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B06-D</t>
+          <t>B05-E</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Arco A6, perna direita</t>
+          <t>Arco A5, perna esquerda</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3.32</v>
+        <v>3.68</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2290,19 +2290,19 @@
         <v>3.6</v>
       </c>
       <c r="J30" t="n">
-        <v>25.1</v>
+        <v>27.9</v>
       </c>
       <c r="K30" t="n">
-        <v>25.1</v>
+        <v>27.9</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Idem perna esquerda</t>
+          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -2310,26 +2310,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Pórtico elíptico A5 (x = 6.45 m)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B07-E</t>
+          <t>B05-C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Arco A7, perna esquerda</t>
+          <t>Arco A5, coroa (segmento superior)</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>2.69</v>
+        <v>3.46</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2351,19 +2351,19 @@
         <v>3.6</v>
       </c>
       <c r="J31" t="n">
-        <v>20.4</v>
+        <v>26.2</v>
       </c>
       <c r="K31" t="n">
-        <v>20.4</v>
+        <v>26.2</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
+          <t>Calandra CNC; talões D03 das terças soldados</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
+          <t>Encaixa nas luvas D02 das duas pernas</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -2371,26 +2371,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Pórtico elíptico A7 (x = 8.75 m)</t>
+          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B07-C</t>
+          <t>B05-D</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Arco A7, coroa (segmento superior)</t>
+          <t>Arco A5, perna direita</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>2.53</v>
+        <v>3.68</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -2412,19 +2412,19 @@
         <v>3.6</v>
       </c>
       <c r="J32" t="n">
-        <v>19.2</v>
+        <v>27.9</v>
       </c>
       <c r="K32" t="n">
-        <v>19.2</v>
+        <v>27.9</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Calandra CNC; talões D03 das terças soldados</t>
+          <t>Idem perna esquerda</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Encaixa nas luvas D02 das duas pernas</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -2432,26 +2432,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
+          <t>Idem</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B07-D</t>
+          <t>B06-E</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Arco A7, perna direita</t>
+          <t>Arco A6, perna esquerda</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>2.69</v>
+        <v>3.32</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -2473,19 +2473,19 @@
         <v>3.6</v>
       </c>
       <c r="J33" t="n">
-        <v>20.4</v>
+        <v>25.1</v>
       </c>
       <c r="K33" t="n">
-        <v>20.4</v>
+        <v>25.1</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Idem perna esquerda</t>
+          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -2493,26 +2493,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Pórtico elíptico A6 (x = 7.65 m)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>B06-C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quadro da cauda (anel Ø60,3 + 3 barras radiais)</t>
+          <t>Arco A6, coroa (segmento superior)</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>7.5</v>
+        <v>3.12</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tubo Ø60,3 x 3,0</t>
+          <t>Tubo Ø88,9 x 3,6 calandrado (elipse)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2531,22 +2531,22 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
-        <v>31.8</v>
+        <v>23.6</v>
       </c>
       <c r="K34" t="n">
-        <v>31.8</v>
+        <v>23.6</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Solda em gabarito</t>
+          <t>Calandra CNC; talões D03 das terças soldados</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Chapa D01 (2) + luva D02 no arco A7</t>
+          <t>Encaixa nas luvas D02 das duas pernas</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -2554,26 +2554,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Fecha a ponta da cauda e ancora a tampa de membrana</t>
+          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B06-D</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Terça longitudinal, trecho de 1,20 m</t>
+          <t>Arco A6, perna direita</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1.2</v>
+        <v>3.32</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tubo Ø48,3 x 3,0</t>
+          <t>Tubo Ø88,9 x 3,6 calandrado (elipse)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2592,49 +2592,49 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
-        <v>4.4</v>
+        <v>25.1</v>
       </c>
       <c r="K35" t="n">
-        <v>216.6</v>
+        <v>25.1</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Corte + ponteiras rosqueadas M16 soldadas nas duas pontas</t>
+          <t>Idem perna esquerda</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Rosca M16 no talão D03 + porca e contraporca</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Travamento longitudinal dos arcos e apoio do isolamento</t>
+          <t>Idem</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>B07-E</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Terça longitudinal, trecho da cauda (1,10 e 0,85 m)</t>
+          <t>Arco A7, perna esquerda</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0.98</v>
+        <v>2.69</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tubo Ø48,3 x 3,0</t>
+          <t>Tubo Ø88,9 x 3,6 calandrado (elipse)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2653,59 +2653,59 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
-        <v>3.7</v>
+        <v>20.4</v>
       </c>
       <c r="K36" t="n">
-        <v>51.6</v>
+        <v>20.4</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Calandra CNC por gabarito; ponta com luva D02 soldada</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Luva D02 com 4 M12 8.8 + pino Ø6; pé com chapa D01 + 4 M16</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Idem, entre A6, A7 e o quadro da cauda</t>
+          <t>Pórtico elíptico A7 (x = 8.75 m)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>B07-C</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Espinha de Luz (treliça plana 300 mm), 2 trechos de 2,35 m</t>
+          <t>Arco A7, coroa (segmento superior)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="E37" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Banzos Ø42,4 x 3,0 + diagonais Ø26,9 x 2,6</t>
+          <t>Tubo Ø88,9 x 3,6 calandrado (elipse)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2714,49 +2714,49 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
         <v>19.2</v>
       </c>
       <c r="K37" t="n">
-        <v>38.5</v>
+        <v>19.2</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Solda em gabarito; berços de vidro D08</t>
+          <t>Calandra CNC; talões D03 das terças soldados</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Berço D06 nas coroas A1 a A5 + 2 M12 cada</t>
+          <t>Encaixa nas luvas D02 das duas pernas</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Apoia os 4 vidros da claraboia e trava a cumeeira</t>
+          <t>Fecha o pórtico; recebe a Espinha de Luz (A1 a A5)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>B07-D</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cabo de contraventamento em X</t>
+          <t>Arco A7, perna direita</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>2.69</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -2766,92 +2766,92 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cabo de aço inox AISI 316 Ø8 mm 7 x 19</t>
+          <t>Tubo Ø88,9 x 3,6 calandrado (elipse)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>inox 316</t>
+          <t>ASTM A500 Gr. B galv.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
-        <v>2.2</v>
+        <v>20.4</v>
       </c>
       <c r="K38" t="n">
-        <v>17.3</v>
+        <v>20.4</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Terminais prensados com olhal</t>
+          <t>Idem perna esquerda</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Olhal D05 + manilha + esticador M12 inox</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Resiste ao vento longitudinal nos vãos A0-A1 e A5-A6</t>
+          <t>Idem</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chapa de base dos arcos (200 x 150 x 10) com 2 enrijecedores</t>
+          <t>Quadro da cauda (anel Ø60,3 + 3 barras radiais)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2</v>
+        <v>7.5</v>
       </c>
       <c r="E39" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chapa A36 + enrijecedores 80 x 60 x 8</t>
+          <t>Tubo Ø60,3 x 3,0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ASTM A36 galv.</t>
+          <t>ASTM A500 Gr. B galv.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>2.6</v>
+        <v>31.8</v>
       </c>
       <c r="K39" t="n">
-        <v>46.8</v>
+        <v>31.8</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Corte plasma + solda de fábrica no pé do arco</t>
+          <t>Solda em gabarito</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>4 chumbadores M16 8.8 na viga de borda</t>
+          <t>Chapa D01 (2) + luva D02 no arco A7</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -2859,26 +2859,26 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Engasta o arco no quadro do deck</t>
+          <t>Fecha a ponta da cauda e ancora a tampa de membrana</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Luva interna de emenda Ø76,1 x 200 (4 furos Ø13)</t>
+          <t>Terça longitudinal, trecho de 1,20 m</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tubo Ø76,1 x 3,6</t>
+          <t>Tubo Ø48,3 x 3,0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2897,364 +2897,364 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="K40" t="n">
-        <v>20.6</v>
+        <v>216.6</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Corte + furação; soldada dentro da perna</t>
+          <t>Corte + ponteiras rosqueadas M16 soldadas nas duas pontas</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Encaixe macho-fêmea + 4 M12 8.8 + pino de segurança Ø6</t>
+          <t>Rosca M16 no talão D03 + porca e contraporca</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Emenda de fábrica/campo entre perna e coroa</t>
+          <t>Travamento longitudinal dos arcos e apoio do isolamento</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Talão de terça (chapa 8 mm com furo Ø17)</t>
+          <t>Terça longitudinal, trecho da cauda (1,10 e 0,85 m)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="D41" t="n">
-        <v>0.06</v>
+        <v>0.98</v>
       </c>
       <c r="E41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chapa A36</t>
+          <t>Tubo Ø48,3 x 3,0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ASTM A36 galv.</t>
+          <t>ASTM A500 Gr. B galv.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1</v>
+        <v>3.7</v>
       </c>
       <c r="K41" t="n">
-        <v>8.4</v>
+        <v>51.6</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Corte laser + solda de fábrica nos arcos</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Recebe a ponteira M16 das terças</t>
+          <t>Idem</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Ponto de fixação das terças</t>
+          <t>Idem, entre A6, A7 e o quadro da cauda</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chapa de topo dos cabeçotes (150 x 150 x 8, 4 furos)</t>
+          <t>Espinha de Luz (treliça plana 300 mm), 2 trechos de 2,35 m</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>0.15</v>
+        <v>2.35</v>
       </c>
       <c r="E42" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chapa A36</t>
+          <t>Banzos Ø42,4 x 3,0 + diagonais Ø26,9 x 2,6</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ASTM A36 galv.</t>
+          <t>ASTM A500 Gr. B galv.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
-        <v>1.4</v>
+        <v>19.2</v>
       </c>
       <c r="K42" t="n">
-        <v>61.6</v>
+        <v>38.5</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Corte + furação (fornecida com o cabeçote)</t>
+          <t>Solda em gabarito; berços de vidro D08</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>4 M12 8.8 na mesa da viga U</t>
+          <t>Berço D06 nas coroas A1 a A5 + 2 M12 cada</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Liga a fundação ao quadro do deck</t>
+          <t>Apoia os 4 vidros da claraboia e trava a cumeeira</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Olhal para cabo (chapa 10 mm, furo Ø14)</t>
+          <t>Cabo de contraventamento em X</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>0.08</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chapa A36</t>
+          <t>Cabo de aço inox AISI 316 Ø8 mm 7 x 19</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ASTM A36 galv.</t>
+          <t>inox 316</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="K43" t="n">
-        <v>2.4</v>
+        <v>17.3</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Corte laser + solda de fábrica nos arcos</t>
+          <t>Terminais prensados com olhal</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Manilha inox</t>
+          <t>Olhal D05 + manilha + esticador M12 inox</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Ancoragem dos cabos em X</t>
+          <t>Resiste ao vento longitudinal nos vãos A0-A1 e A5-A6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chapa de emenda das vigas (120 x 140 x 6, 4 furos)</t>
+          <t>Chapa de base dos arcos (200 x 150 x 10) com 2 enrijecedores</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D44" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="E44" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F44" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chapa A36 + enrijecedores 80 x 60 x 8</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ASTM A36 galv.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K44" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Corte plasma + solda de fábrica no pé do arco</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4 chumbadores M16 8.8 na viga de borda</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
         <v>6</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Chapa A36</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>ASTM A36 galv.</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>6</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K44" t="n">
-        <v>16</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Corte + furação</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>4 M12 8.8 por face</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>3</v>
-      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Emenda das vigas longitudinais e de borda</t>
+          <t>Engasta o arco no quadro do deck</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cantoneira de cruzamento 75 x 75 x 6 x 140</t>
+          <t>Luva interna de emenda Ø76,1 x 200 (4 furos Ø13)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D45" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="E45" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tubo Ø76,1 x 3,6</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ASTM A500 Gr. B galv.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Corte + furação; soldada dentro da perna</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Encaixe macho-fêmea + 4 M12 8.8 + pino de segurança Ø6</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
         <v>6</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Cantoneira laminada</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>ASTM A36 galv.</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K45" t="n">
-        <v>54</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Corte + furação</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2 M12 em cada aba</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>3</v>
-      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Ligação viga transversal x longitudinal</t>
+          <t>Emenda de fábrica/campo entre perna e coroa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Berço de vidro da espinha (chapa 5 mm dobrada + EPDM)</t>
+          <t>Talão de terça (chapa 8 mm com furo Ø17)</t>
         </is>
       </c>
       <c r="C46" t="n">
+        <v>56</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E46" t="n">
+        <v>40</v>
+      </c>
+      <c r="F46" t="n">
         <v>8</v>
       </c>
-      <c r="D46" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E46" t="n">
-        <v>60</v>
-      </c>
-      <c r="F46" t="n">
-        <v>5</v>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chapa A36 dobrada</t>
+          <t>Chapa A36</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3263,425 +3263,425 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Corte + dobra + solda na treliça</t>
+          <t>Corte laser + solda de fábrica nos arcos</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Vidro apoiado em EPDM + presilha inox M6</t>
+          <t>Recebe a ponteira M16 das terças</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Apoio dos painéis de vidro da claraboia</t>
+          <t>Ponto de fixação das terças</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Perfil duplo keder de alumínio (por arco, em 3 trechos)</t>
+          <t>Chapa de topo dos cabeçotes (150 x 150 x 8, 4 furos)</t>
         </is>
       </c>
       <c r="C47" t="n">
+        <v>44</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E47" t="n">
+        <v>150</v>
+      </c>
+      <c r="F47" t="n">
         <v>8</v>
       </c>
-      <c r="D47" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="E47" t="n">
-        <v>70</v>
-      </c>
-      <c r="F47" t="n">
-        <v>24</v>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alumínio 6060-T5 extrudado, calandrado</t>
+          <t>Chapa A36</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>alumínio</t>
+          <t>ASTM A36 galv.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>9.6</v>
+        <v>1.4</v>
       </c>
       <c r="K47" t="n">
-        <v>76.90000000000001</v>
+        <v>61.6</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Extrusão + calandra</t>
+          <t>Corte + furação (fornecida com o cabeçote)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Presilha inox E03 a cada 300 mm sobre o arco</t>
+          <t>4 M12 8.8 na mesa da viga U</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Recebe o cordão keder dos painéis de membrana</t>
+          <t>Liga a fundação ao quadro do deck</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Perfil de arremate de base com calha oculta 80 x 60</t>
+          <t>Olhal para cabo (chapa 10 mm, furo Ø14)</t>
         </is>
       </c>
       <c r="C48" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E48" t="n">
+        <v>50</v>
+      </c>
+      <c r="F48" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chapa A36</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ASTM A36 galv.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>10</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Corte laser + solda de fábrica nos arcos</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Manilha inox</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
         <v>6</v>
       </c>
-      <c r="D48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" t="n">
-        <v>80</v>
-      </c>
-      <c r="F48" t="n">
-        <v>60</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Alumínio 6063 extrudado</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>alumínio</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K48" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Extrusão + corte</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Parafuso inox M8 @400 no trilho A07/A08</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>8</v>
-      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Arremate inferior da membrana e drenagem</t>
+          <t>Ancoragem dos cabos em X</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Presilha inox do keder (3 mm) + parafuso M8 x 30</t>
+          <t>Chapa de emenda das vigas (120 x 140 x 6, 4 furos)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="D49" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="E49" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="F49" t="n">
+        <v>6</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chapa A36</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ASTM A36 galv.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>6</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K49" t="n">
+        <v>16</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Corte + furação</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>4 M12 8.8 por face</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
         <v>3</v>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Inox 304</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>inox 304</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>3</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>9</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Estampada</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>M8 inox rosqueado em inserto no arco</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>8</v>
-      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Fixa o perfil keder ao arco</t>
+          <t>Emenda das vigas longitudinais e de borda</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trilho do forro tensionado (harpão) 40 x 20</t>
+          <t>Cantoneira de cruzamento 75 x 75 x 6 x 140</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D50" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E50" t="n">
+        <v>75</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cantoneira laminada</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ASTM A36 galv.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>6</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K50" t="n">
+        <v>54</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Corte + furação</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2 M12 em cada aba</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
         <v>3</v>
       </c>
-      <c r="E50" t="n">
-        <v>40</v>
-      </c>
-      <c r="F50" t="n">
-        <v>20</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Alumínio 6063</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>alumínio</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Extrusão + corte</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Rebite ou M6 no talão secundário das terças</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>10</v>
-      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Fixa o forro tensionado</t>
+          <t>Ligação viga transversal x longitudinal</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Requadro da Janela Olho (madeira laminada, 220 mm)</t>
+          <t>Berço de vidro da espinha (chapa 5 mm dobrada + EPDM)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
-        <v>1.6</v>
+        <v>0.12</v>
       </c>
       <c r="E51" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="F51" t="n">
-        <v>220</v>
+        <v>5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lâminas de eucalipto colado</t>
+          <t>Chapa A36 dobrada</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>madeira laminada</t>
+          <t>ASTM A36 galv.</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>220</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="K51" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Usinagem CNC 5 eixos + verniz</t>
+          <t>Corte + dobra + solda na treliça</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Parafusos inox M8 nos anéis de reforço E06 + selante PU</t>
+          <t>Vidro apoiado em EPDM + presilha inox M6</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Transição concha curva x vidro plano</t>
+          <t>Apoio dos painéis de vidro da claraboia</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Anel de reforço da janela (chapa 3 mm curvada)</t>
+          <t>Perfil duplo keder de alumínio (por arco, em 3 trechos)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
-        <v>4.2</v>
+        <v>10.68</v>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chapa A36 curvada</t>
+          <t>Alumínio 6060-T5 extrudado, calandrado</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ASTM A36 galv.</t>
+          <t>alumínio</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>3</v>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="K52" t="n">
-        <v>36</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Corte laser + calandra + solda nas terças</t>
+          <t>Extrusão + calandra</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Solda de fábrica</t>
+          <t>Presilha inox E03 a cada 300 mm sobre o arco</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Distribui a tensão da membrana ao redor do Olho</t>
+          <t>Recebe o cordão keder dos painéis de membrana</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Anel de alumínio da fachada 120 x 60 (2 metades)</t>
+          <t>Perfil de arremate de base com calha oculta 80 x 60</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F53" t="n">
         <v>60</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alumínio 6063-T6 calandrado</t>
+          <t>Alumínio 6063 extrudado</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3690,150 +3690,455 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>12.8</v>
+        <v>4.8</v>
       </c>
       <c r="K53" t="n">
-        <v>25.5</v>
+        <v>28.8</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Calandra + usinagem</t>
+          <t>Extrusão + corte</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Parafuso M8 @400 + fita EPDM sobre o anel B00</t>
+          <t>Parafuso inox M8 @400 no trilho A07/A08</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Base da esquadria da fachada inclinada</t>
+          <t>Arremate inferior da membrana e drenagem</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Estaca helicoidal Ø76 x 3,6, hélice Ø300, L 2,0 m</t>
+          <t>Presilha inox do keder (3 mm) + parafuso M8 x 30</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>0.04</v>
       </c>
       <c r="E54" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Inox 304</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>inox 304</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" t="n">
         <v>0</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Tubo Ø76,1 x 3,6 + hélice chapa 8 mm</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>ASTM A500 / A36 galv.</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J54" t="n">
-        <v>18.4</v>
-      </c>
       <c r="K54" t="n">
-        <v>808.7</v>
+        <v>9</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Solda da hélice + galvanização (compra)</t>
+          <t>Estampada</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Rosca M30 do cabeçote F02</t>
+          <t>M8 inox rosqueado em inserto no arco</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Fundação removível sem escavação</t>
+          <t>Fixa o perfil keder ao arco</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Trilho do forro tensionado (harpão) 40 x 20</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>22</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>40</v>
+      </c>
+      <c r="F55" t="n">
+        <v>20</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alumínio 6063</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>alumínio</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Extrusão + corte</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Rebite ou M6 no talão secundário das terças</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>10</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Fixa o forro tensionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Requadro da Janela Olho (madeira laminada, 220 mm)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E56" t="n">
+        <v>950</v>
+      </c>
+      <c r="F56" t="n">
+        <v>220</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lâminas de eucalipto colado</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>madeira laminada</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>220</v>
+      </c>
+      <c r="J56" t="n">
+        <v>9</v>
+      </c>
+      <c r="K56" t="n">
+        <v>54</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Usinagem CNC 5 eixos + verniz</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Parafusos inox M8 nos anéis de reforço E06 + selante PU</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>11</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Transição concha curva x vidro plano</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Anel de reforço da janela (chapa 3 mm curvada)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>60</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Chapa A36 curvada</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ASTM A36 galv.</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>6</v>
+      </c>
+      <c r="K57" t="n">
+        <v>36</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Corte laser + calandra + solda nas terças</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Solda de fábrica</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>6</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Distribui a tensão da membrana ao redor do Olho</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Anel de alumínio da fachada 120 x 60 (2 metades)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>120</v>
+      </c>
+      <c r="F58" t="n">
+        <v>60</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alumínio 6063-T6 calandrado</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>alumínio</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K58" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Calandra + usinagem</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Parafuso M8 @400 + fita EPDM sobre o anel B00</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>11</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Base da esquadria da fachada inclinada</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Estaca helicoidal Ø76 x 3,6, hélice Ø300, L 2,0 m</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>44</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>300</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tubo Ø76,1 x 3,6 + hélice chapa 8 mm</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ASTM A500 / A36 galv.</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J59" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K59" t="n">
+        <v>808.7</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Solda da hélice + galvanização (compra)</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Rosca M30 do cabeçote F02</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Fundação removível sem escavação</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>F02</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Cabeçote ajustável rosqueado (curso 150 mm) + chapa D04</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C60" t="n">
         <v>44</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D60" t="n">
         <v>0.25</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E60" t="n">
         <v>150</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F60" t="n">
         <v>8</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Barra roscada M30 + chapa</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>aço galv.</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="I60" t="n">
         <v>8</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J60" t="n">
         <v>2.2</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K60" t="n">
         <v>96.8</v>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>Compra</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>Rosca M30 + contraporca; 4 M12 na viga</t>
         </is>
       </c>
-      <c r="N55" t="n">
+      <c r="N60" t="n">
         <v>2</v>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>Nivelamento fino do deck</t>
         </is>
@@ -13490,25 +13795,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1128</v>
+        <v>1235</v>
       </c>
       <c r="E2" t="n">
         <v>9.94</v>
       </c>
       <c r="F2" t="n">
-        <v>11207.81</v>
+        <v>12270.96</v>
       </c>
       <c r="G2" t="n">
         <v>10.8</v>
       </c>
       <c r="H2" t="n">
-        <v>12182.4</v>
+        <v>13338</v>
       </c>
       <c r="I2" t="n">
         <v>11.66</v>
       </c>
       <c r="J2" t="n">
-        <v>13156.99</v>
+        <v>14405.04</v>
       </c>
     </row>
     <row r="3">
@@ -13604,25 +13909,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1340</v>
+        <v>1447</v>
       </c>
       <c r="E5" t="n">
         <v>5.6</v>
       </c>
       <c r="F5" t="n">
-        <v>7504</v>
+        <v>8103.2</v>
       </c>
       <c r="G5" t="n">
         <v>7.4</v>
       </c>
       <c r="H5" t="n">
-        <v>9916</v>
+        <v>10707.8</v>
       </c>
       <c r="I5" t="n">
         <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>9916</v>
+        <v>10707.8</v>
       </c>
     </row>
     <row r="6">
@@ -13642,7 +13947,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>938</v>
+        <v>1013</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13654,13 +13959,13 @@
         <v>4.9</v>
       </c>
       <c r="H6" t="n">
-        <v>4596.2</v>
+        <v>4963.7</v>
       </c>
       <c r="I6" t="n">
         <v>5.63</v>
       </c>
       <c r="J6" t="n">
-        <v>5285.63</v>
+        <v>5708.26</v>
       </c>
     </row>
     <row r="7">
@@ -13794,25 +14099,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E10" t="n">
         <v>146.2</v>
       </c>
       <c r="F10" t="n">
-        <v>16813</v>
+        <v>18128.8</v>
       </c>
       <c r="G10" t="n">
         <v>215</v>
       </c>
       <c r="H10" t="n">
-        <v>24725</v>
+        <v>26660</v>
       </c>
       <c r="I10" t="n">
         <v>311.75</v>
       </c>
       <c r="J10" t="n">
-        <v>35851.25</v>
+        <v>38657</v>
       </c>
     </row>
     <row r="11">
@@ -13832,25 +14137,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E11" t="n">
         <v>88.2</v>
       </c>
       <c r="F11" t="n">
-        <v>10143</v>
+        <v>10936.8</v>
       </c>
       <c r="G11" t="n">
         <v>98</v>
       </c>
       <c r="H11" t="n">
-        <v>11270</v>
+        <v>12152</v>
       </c>
       <c r="I11" t="n">
         <v>107.8</v>
       </c>
       <c r="J11" t="n">
-        <v>12397</v>
+        <v>13367.2</v>
       </c>
     </row>
     <row r="12">
@@ -13946,25 +14251,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E14" t="n">
         <v>30.6</v>
       </c>
       <c r="F14" t="n">
-        <v>3060</v>
+        <v>3304.8</v>
       </c>
       <c r="G14" t="n">
         <v>36</v>
       </c>
       <c r="H14" t="n">
-        <v>3600</v>
+        <v>3888</v>
       </c>
       <c r="I14" t="n">
         <v>36</v>
       </c>
       <c r="J14" t="n">
-        <v>3600</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="15">
@@ -13984,25 +14289,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>1700</v>
+        <v>1836</v>
       </c>
       <c r="G15" t="n">
         <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>1700</v>
+        <v>1836</v>
       </c>
       <c r="I15" t="n">
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>1700</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="16">
@@ -14022,25 +14327,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E16" t="n">
         <v>17.6</v>
       </c>
       <c r="F16" t="n">
-        <v>1760</v>
+        <v>1900.8</v>
       </c>
       <c r="G16" t="n">
         <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>2200</v>
+        <v>2376</v>
       </c>
       <c r="I16" t="n">
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>2200</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="17">
@@ -14060,25 +14365,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E17" t="n">
         <v>172.25</v>
       </c>
       <c r="F17" t="n">
-        <v>16363.75</v>
+        <v>17741.75</v>
       </c>
       <c r="G17" t="n">
         <v>265</v>
       </c>
       <c r="H17" t="n">
-        <v>25175</v>
+        <v>27295</v>
       </c>
       <c r="I17" t="n">
         <v>344.5</v>
       </c>
       <c r="J17" t="n">
-        <v>32727.5</v>
+        <v>35483.5</v>
       </c>
     </row>
     <row r="18">
@@ -15232,15 +15537,15 @@
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="n">
-        <v>352665.318</v>
+        <v>358336.87</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="n">
-        <v>498571.6</v>
+        <v>506423.5</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="n">
-        <v>674416.072</v>
+        <v>684010.495</v>
       </c>
     </row>
   </sheetData>
@@ -15760,13 +16065,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>352665.32</v>
+        <v>358336.87</v>
       </c>
       <c r="C2" t="n">
-        <v>498571.6</v>
+        <v>506423.5</v>
       </c>
       <c r="D2" t="n">
-        <v>674416.0699999999</v>
+        <v>684010.49</v>
       </c>
     </row>
     <row r="3">
@@ -15856,13 +16161,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>229489.52</v>
+        <v>235161.07</v>
       </c>
       <c r="C8" t="n">
-        <v>323896.6</v>
+        <v>331748.5</v>
       </c>
       <c r="D8" t="n">
-        <v>425579.32</v>
+        <v>435173.75</v>
       </c>
     </row>
     <row r="9">
@@ -15888,13 +16193,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53403.99</v>
+        <v>54084.57</v>
       </c>
       <c r="C10" t="n">
-        <v>71854.85000000001</v>
+        <v>72797.08</v>
       </c>
       <c r="D10" t="n">
-        <v>94040.78</v>
+        <v>95192.11</v>
       </c>
     </row>
     <row r="11">
@@ -15904,13 +16209,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44503.32</v>
+        <v>45070.48</v>
       </c>
       <c r="C11" t="n">
-        <v>47903.23</v>
+        <v>48531.38</v>
       </c>
       <c r="D11" t="n">
-        <v>62693.85</v>
+        <v>63461.41</v>
       </c>
     </row>
     <row r="12">
@@ -15936,13 +16241,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>782940.55</v>
+        <v>789859.84</v>
       </c>
       <c r="C13" t="n">
-        <v>958548.48</v>
+        <v>967970.76</v>
       </c>
       <c r="D13" t="n">
-        <v>1180407.78</v>
+        <v>1191921.09</v>
       </c>
     </row>
     <row r="14">
@@ -15952,13 +16257,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>542940.55</v>
+        <v>549859.84</v>
       </c>
       <c r="C14" t="n">
-        <v>718548.48</v>
+        <v>727970.76</v>
       </c>
       <c r="D14" t="n">
-        <v>940407.78</v>
+        <v>951921.09</v>
       </c>
     </row>
     <row r="15">
@@ -15968,13 +16273,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10037.7</v>
+        <v>10126.41</v>
       </c>
       <c r="C15" t="n">
-        <v>12289.08</v>
+        <v>12409.88</v>
       </c>
       <c r="D15" t="n">
-        <v>15133.43</v>
+        <v>15281.04</v>
       </c>
     </row>
     <row r="16">
@@ -15984,13 +16289,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16311.26</v>
+        <v>16455.41</v>
       </c>
       <c r="C16" t="n">
-        <v>19969.76</v>
+        <v>20166.06</v>
       </c>
       <c r="D16" t="n">
-        <v>24591.83</v>
+        <v>24831.69</v>
       </c>
     </row>
   </sheetData>
@@ -16064,7 +16369,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>498571.6</v>
+        <v>506423.5</v>
       </c>
       <c r="C2" t="n">
         <v>74618.8</v>
@@ -16073,16 +16378,16 @@
         <v>25600</v>
       </c>
       <c r="E2" t="n">
-        <v>119758.08</v>
+        <v>121328.46</v>
       </c>
       <c r="F2" t="n">
         <v>240000</v>
       </c>
       <c r="G2" t="n">
-        <v>958548.48</v>
+        <v>967970.76</v>
       </c>
       <c r="H2" t="n">
-        <v>12289.08</v>
+        <v>12409.88</v>
       </c>
     </row>
     <row r="3">
@@ -16090,7 +16395,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>472276.2</v>
+        <v>479680.14</v>
       </c>
       <c r="C3" t="n">
         <v>67482.3</v>
@@ -16099,16 +16404,16 @@
         <v>22668</v>
       </c>
       <c r="E3" t="n">
-        <v>95612.5</v>
+        <v>96871.17</v>
       </c>
       <c r="F3" t="n">
         <v>48000</v>
       </c>
       <c r="G3" t="n">
-        <v>706039</v>
+        <v>714701.6</v>
       </c>
       <c r="H3" t="n">
-        <v>9051.780000000001</v>
+        <v>9162.84</v>
       </c>
     </row>
     <row r="4">
@@ -16116,7 +16421,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>455383.23</v>
+        <v>462496.24</v>
       </c>
       <c r="C4" t="n">
         <v>63167.86</v>
@@ -16125,16 +16430,16 @@
         <v>21221</v>
       </c>
       <c r="E4" t="n">
-        <v>80965.81</v>
+        <v>82032.75999999999</v>
       </c>
       <c r="F4" t="n">
         <v>24000</v>
       </c>
       <c r="G4" t="n">
-        <v>644737.9</v>
+        <v>652917.86</v>
       </c>
       <c r="H4" t="n">
-        <v>8265.870000000001</v>
+        <v>8370.74</v>
       </c>
     </row>
     <row r="5">
@@ -16142,7 +16447,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>426629.89</v>
+        <v>433184.2</v>
       </c>
       <c r="C5" t="n">
         <v>56972.04</v>
@@ -16151,16 +16456,16 @@
         <v>19106</v>
       </c>
       <c r="E5" t="n">
-        <v>65352.03</v>
+        <v>66204.09</v>
       </c>
       <c r="F5" t="n">
         <v>4800</v>
       </c>
       <c r="G5" t="n">
-        <v>572859.96</v>
+        <v>580266.33</v>
       </c>
       <c r="H5" t="n">
-        <v>7344.36</v>
+        <v>7439.31</v>
       </c>
     </row>
   </sheetData>

--- a/projects/zion-glamping-line/interno/ZION_ORCAMENTO_SC_Casulo_Safari_Lodge.xlsx
+++ b/projects/zion-glamping-line/interno/ZION_ORCAMENTO_SC_Casulo_Safari_Lodge.xlsx
@@ -14099,25 +14099,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E10" t="n">
         <v>146.2</v>
       </c>
       <c r="F10" t="n">
-        <v>18128.8</v>
+        <v>18567.4</v>
       </c>
       <c r="G10" t="n">
         <v>215</v>
       </c>
       <c r="H10" t="n">
-        <v>26660</v>
+        <v>27305</v>
       </c>
       <c r="I10" t="n">
         <v>311.75</v>
       </c>
       <c r="J10" t="n">
-        <v>38657</v>
+        <v>39592.25</v>
       </c>
     </row>
     <row r="11">
@@ -14137,25 +14137,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E11" t="n">
         <v>88.2</v>
       </c>
       <c r="F11" t="n">
-        <v>10936.8</v>
+        <v>11201.4</v>
       </c>
       <c r="G11" t="n">
         <v>98</v>
       </c>
       <c r="H11" t="n">
-        <v>12152</v>
+        <v>12446</v>
       </c>
       <c r="I11" t="n">
         <v>107.8</v>
       </c>
       <c r="J11" t="n">
-        <v>13367.2</v>
+        <v>13690.6</v>
       </c>
     </row>
     <row r="12">
@@ -14251,25 +14251,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E14" t="n">
         <v>30.6</v>
       </c>
       <c r="F14" t="n">
-        <v>3304.8</v>
+        <v>3366</v>
       </c>
       <c r="G14" t="n">
         <v>36</v>
       </c>
       <c r="H14" t="n">
-        <v>3888</v>
+        <v>3960</v>
       </c>
       <c r="I14" t="n">
         <v>36</v>
       </c>
       <c r="J14" t="n">
-        <v>3888</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="15">
@@ -14289,25 +14289,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>1836</v>
+        <v>1870</v>
       </c>
       <c r="G15" t="n">
         <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>1836</v>
+        <v>1870</v>
       </c>
       <c r="I15" t="n">
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>1836</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="16">
@@ -14327,25 +14327,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E16" t="n">
         <v>17.6</v>
       </c>
       <c r="F16" t="n">
-        <v>1900.8</v>
+        <v>1936</v>
       </c>
       <c r="G16" t="n">
         <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>2376</v>
+        <v>2420</v>
       </c>
       <c r="I16" t="n">
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>2376</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="17">
@@ -14365,25 +14365,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E17" t="n">
         <v>172.25</v>
       </c>
       <c r="F17" t="n">
-        <v>17741.75</v>
+        <v>18086.25</v>
       </c>
       <c r="G17" t="n">
         <v>265</v>
       </c>
       <c r="H17" t="n">
-        <v>27295</v>
+        <v>27825</v>
       </c>
       <c r="I17" t="n">
         <v>344.5</v>
       </c>
       <c r="J17" t="n">
-        <v>35483.5</v>
+        <v>36172.5</v>
       </c>
     </row>
     <row r="18">
@@ -15537,15 +15537,15 @@
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="n">
-        <v>358336.87</v>
+        <v>359514.97</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="n">
-        <v>506423.5</v>
+        <v>508042.5</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="n">
-        <v>684010.495</v>
+        <v>686108.145</v>
       </c>
     </row>
   </sheetData>
@@ -16065,13 +16065,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>358336.87</v>
+        <v>359514.97</v>
       </c>
       <c r="C2" t="n">
-        <v>506423.5</v>
+        <v>508042.5</v>
       </c>
       <c r="D2" t="n">
-        <v>684010.49</v>
+        <v>686108.15</v>
       </c>
     </row>
     <row r="3">
@@ -16161,13 +16161,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>235161.07</v>
+        <v>236339.17</v>
       </c>
       <c r="C8" t="n">
-        <v>331748.5</v>
+        <v>333367.5</v>
       </c>
       <c r="D8" t="n">
-        <v>435173.75</v>
+        <v>437271.4</v>
       </c>
     </row>
     <row r="9">
@@ -16193,13 +16193,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54084.57</v>
+        <v>54225.95</v>
       </c>
       <c r="C10" t="n">
-        <v>72797.08</v>
+        <v>72991.36</v>
       </c>
       <c r="D10" t="n">
-        <v>95192.11</v>
+        <v>95443.83</v>
       </c>
     </row>
     <row r="11">
@@ -16209,13 +16209,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45070.48</v>
+        <v>45188.29</v>
       </c>
       <c r="C11" t="n">
-        <v>48531.38</v>
+        <v>48660.9</v>
       </c>
       <c r="D11" t="n">
-        <v>63461.41</v>
+        <v>63629.22</v>
       </c>
     </row>
     <row r="12">
@@ -16241,13 +16241,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>789859.84</v>
+        <v>791297.13</v>
       </c>
       <c r="C13" t="n">
-        <v>967970.76</v>
+        <v>969913.5600000001</v>
       </c>
       <c r="D13" t="n">
-        <v>1191921.09</v>
+        <v>1194438.27</v>
       </c>
     </row>
     <row r="14">
@@ -16257,13 +16257,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>549859.84</v>
+        <v>551297.13</v>
       </c>
       <c r="C14" t="n">
-        <v>727970.76</v>
+        <v>729913.5600000001</v>
       </c>
       <c r="D14" t="n">
-        <v>951921.09</v>
+        <v>954438.27</v>
       </c>
     </row>
     <row r="15">
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10126.41</v>
+        <v>10144.83</v>
       </c>
       <c r="C15" t="n">
-        <v>12409.88</v>
+        <v>12434.79</v>
       </c>
       <c r="D15" t="n">
-        <v>15281.04</v>
+        <v>15313.31</v>
       </c>
     </row>
     <row r="16">
@@ -16289,13 +16289,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16455.41</v>
+        <v>16485.36</v>
       </c>
       <c r="C16" t="n">
-        <v>20166.06</v>
+        <v>20206.53</v>
       </c>
       <c r="D16" t="n">
-        <v>24831.69</v>
+        <v>24884.13</v>
       </c>
     </row>
   </sheetData>
@@ -16369,7 +16369,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>506423.5</v>
+        <v>508042.5</v>
       </c>
       <c r="C2" t="n">
         <v>74618.8</v>
@@ -16378,16 +16378,16 @@
         <v>25600</v>
       </c>
       <c r="E2" t="n">
-        <v>121328.46</v>
+        <v>121652.26</v>
       </c>
       <c r="F2" t="n">
         <v>240000</v>
       </c>
       <c r="G2" t="n">
-        <v>967970.76</v>
+        <v>969913.5600000001</v>
       </c>
       <c r="H2" t="n">
-        <v>12409.88</v>
+        <v>12434.79</v>
       </c>
     </row>
     <row r="3">
@@ -16395,7 +16395,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>479680.14</v>
+        <v>481201.99</v>
       </c>
       <c r="C3" t="n">
         <v>67482.3</v>
@@ -16404,16 +16404,16 @@
         <v>22668</v>
       </c>
       <c r="E3" t="n">
-        <v>96871.17</v>
+        <v>97129.89</v>
       </c>
       <c r="F3" t="n">
         <v>48000</v>
       </c>
       <c r="G3" t="n">
-        <v>714701.6</v>
+        <v>716482.1800000001</v>
       </c>
       <c r="H3" t="n">
-        <v>9162.84</v>
+        <v>9185.67</v>
       </c>
     </row>
     <row r="4">
@@ -16421,7 +16421,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>462496.24</v>
+        <v>463953.34</v>
       </c>
       <c r="C4" t="n">
         <v>63167.86</v>
@@ -16430,16 +16430,16 @@
         <v>21221</v>
       </c>
       <c r="E4" t="n">
-        <v>82032.75999999999</v>
+        <v>82251.33</v>
       </c>
       <c r="F4" t="n">
         <v>24000</v>
       </c>
       <c r="G4" t="n">
-        <v>652917.86</v>
+        <v>654593.53</v>
       </c>
       <c r="H4" t="n">
-        <v>8370.74</v>
+        <v>8392.219999999999</v>
       </c>
     </row>
     <row r="5">
@@ -16447,7 +16447,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>433184.2</v>
+        <v>434511.78</v>
       </c>
       <c r="C5" t="n">
         <v>56972.04</v>
@@ -16456,16 +16456,16 @@
         <v>19106</v>
       </c>
       <c r="E5" t="n">
-        <v>66204.09</v>
+        <v>66376.67999999999</v>
       </c>
       <c r="F5" t="n">
         <v>4800</v>
       </c>
       <c r="G5" t="n">
-        <v>580266.33</v>
+        <v>581766.49</v>
       </c>
       <c r="H5" t="n">
-        <v>7439.31</v>
+        <v>7458.54</v>
       </c>
     </row>
   </sheetData>
